--- a/PO_ALL_SUPPLIERS_-_see_Supplier_column_20260702.xlsx
+++ b/PO_ALL_SUPPLIERS_-_see_Supplier_column_20260702.xlsx
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J73"/>
+  <dimension ref="A1:J79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -651,13 +651,13 @@
         <v>60</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>92</v>
+        <v>123</v>
       </c>
       <c r="I10" s="7" t="n">
         <v>4.07</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>374.44</v>
+        <v>500.61</v>
       </c>
     </row>
     <row r="11">
@@ -765,13 +765,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I13" s="10" t="n">
         <v>118</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>590</v>
+        <v>708</v>
       </c>
     </row>
     <row r="14">
@@ -955,13 +955,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I18" s="7" t="n">
         <v>5.07</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>152.1</v>
+        <v>167.31</v>
       </c>
     </row>
     <row r="19">
@@ -993,13 +993,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I19" s="10" t="n">
         <v>97</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>97</v>
+        <v>194</v>
       </c>
     </row>
     <row r="20">
@@ -1031,13 +1031,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="I20" s="7" t="n">
         <v>0.53</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>53</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="21">
@@ -1069,13 +1069,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I21" s="10" t="n">
         <v>106.5</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>532.5</v>
+        <v>639</v>
       </c>
     </row>
     <row r="22">
@@ -1107,13 +1107,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I22" s="7" t="n">
         <v>2.01</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>70.34999999999999</v>
+        <v>84.42</v>
       </c>
     </row>
     <row r="23">
@@ -1145,7 +1145,7 @@
         <v>0</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I23" s="10" t="n">
         <v>0</v>
@@ -1183,7 +1183,7 @@
         <v>0</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I24" s="7" t="n">
         <v>0</v>
@@ -1221,7 +1221,7 @@
         <v>0</v>
       </c>
       <c r="H25" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I25" s="10" t="n">
         <v>0</v>
@@ -1263,7 +1263,7 @@
         <v>0</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I26" s="7" t="n">
         <v>0</v>
@@ -1343,13 +1343,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I28" s="7" t="n">
         <v>2.35</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>23.5</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="29">
@@ -1385,7 +1385,7 @@
         <v>0</v>
       </c>
       <c r="H29" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I29" s="10" t="n">
         <v>0</v>
@@ -1427,13 +1427,13 @@
         <v>30</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="I30" s="7" t="n">
         <v>1.53</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>45.9</v>
+        <v>64.26000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1469,13 +1469,13 @@
         <v>6</v>
       </c>
       <c r="H31" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I31" s="10" t="n">
         <v>8</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
     </row>
     <row r="32">
@@ -1511,13 +1511,13 @@
         <v>7</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I32" s="7" t="n">
         <v>5.4</v>
       </c>
       <c r="J32" s="7" t="n">
-        <v>16.2</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="33">
@@ -1587,13 +1587,13 @@
         <v>9</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I34" s="7" t="n">
         <v>3.7</v>
       </c>
       <c r="J34" s="7" t="n">
-        <v>77.7</v>
+        <v>88.8</v>
       </c>
     </row>
     <row r="35">
@@ -1625,13 +1625,13 @@
         <v>3</v>
       </c>
       <c r="H35" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I35" s="10" t="n">
         <v>7</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
     </row>
     <row r="36">
@@ -1667,7 +1667,7 @@
         <v>60</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="I36" s="7" t="n">
         <v>0</v>
@@ -1682,15 +1682,19 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>TAB CELEBIB (CELECOXIB) 200MG SYNERRV</t>
+          <t>TABS BETAMETHASONE 0.5MG Y.S.P.</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>Dr. Nicholas Neelan Jeremiah</t>
-        </is>
-      </c>
-      <c r="D37" s="9" t="inlineStr"/>
+          <t>UMH Pharmacy</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>088-215317  |  umhpharmacy@gmail.com</t>
+        </is>
+      </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
           <t>nan</t>
@@ -1702,16 +1706,16 @@
         </is>
       </c>
       <c r="G37" s="8" t="n">
-        <v>80</v>
+        <v>300</v>
       </c>
       <c r="H37" s="8" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="I37" s="10" t="n">
-        <v>1.08</v>
+        <v>0.11</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>21.6</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="38">
@@ -1720,19 +1724,15 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>MAC DUAL (HEXYLRESORCINOL 2.4MG) ACTION LOZENGES ZIWELL</t>
+          <t>TAB CELEBIB (CELECOXIB) 200MG SYNERRV</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Pahang Pharmacy</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>016-2160526  |  account2@pahangpharmacy.com.my</t>
-        </is>
-      </c>
+          <t>Dr. Nicholas Neelan Jeremiah</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr"/>
       <c r="E38" s="5" t="inlineStr">
         <is>
           <t>nan</t>
@@ -1740,20 +1740,20 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>LOZENGES</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="G38" s="5" t="n">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="H38" s="5" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="I38" s="7" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="J38" s="7" t="n">
-        <v>12.84</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="39">
@@ -1762,15 +1762,19 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>TAB LORADINE (LORATIDINE)10MG Y.S.P.</t>
+          <t>MAC DUAL (HEXYLRESORCINOL 2.4MG) ACTION LOZENGES ZIWELL</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>Permai Polyclinics KK</t>
-        </is>
-      </c>
-      <c r="D39" s="9" t="inlineStr"/>
+          <t>Pahang Pharmacy</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>016-2160526  |  account2@pahangpharmacy.com.my</t>
+        </is>
+      </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
           <t>nan</t>
@@ -1778,20 +1782,20 @@
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>LOZENGES</t>
         </is>
       </c>
       <c r="G39" s="8" t="n">
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="H39" s="8" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="I39" s="10" t="n">
-        <v>0.23</v>
+        <v>1.07</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>2.3</v>
+        <v>25.68</v>
       </c>
     </row>
     <row r="40">
@@ -1800,7 +1804,7 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>EFF GRANULES AVOSODA (SODIUM BICARBONATE) 1.916G/SACHET ABIO</t>
+          <t>TAB LORADINE (LORATIDINE)10MG Y.S.P.</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
@@ -1816,20 +1820,20 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>SACHET</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="G40" s="5" t="n">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="H40" s="5" t="n">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="I40" s="7" t="n">
-        <v>1.01</v>
+        <v>0.23</v>
       </c>
       <c r="J40" s="7" t="n">
-        <v>52.52</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="41">
@@ -1838,7 +1842,7 @@
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>TAB CONCOR (BISOPROLOL) 5MG MERCKS</t>
+          <t>EFF GRANULES AVOSODA (SODIUM BICARBONATE) 1.916G/SACHET ABIO</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
@@ -1854,20 +1858,20 @@
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>SACHET</t>
         </is>
       </c>
       <c r="G41" s="8" t="n">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="H41" s="8" t="n">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="I41" s="10" t="n">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>30.6</v>
+        <v>72.72</v>
       </c>
     </row>
     <row r="42">
@@ -1876,15 +1880,19 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>TAB STORVAS C (ATORVASTATIN) 20MG RANBAXY</t>
+          <t>TAB NORCOLUT (NORETHISTERONE) 5MG PAHANG PHARMACY</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>Permai Polyclinics KK</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr"/>
+          <t>Pharmex</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>088-724989</t>
+        </is>
+      </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
           <t>nan</t>
@@ -1899,13 +1907,13 @@
         <v>20</v>
       </c>
       <c r="H42" s="5" t="n">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="I42" s="7" t="n">
-        <v>0.68</v>
+        <v>0.5</v>
       </c>
       <c r="J42" s="7" t="n">
-        <v>54.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -1914,15 +1922,19 @@
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>TAB DIAPO (DIAZEPAM) 5MG DUOPHARMA</t>
+          <t>SYR RETORIN (ERYTHROMYCIN) 200MG/5ML 60ML SM PHARMA</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>Permai Polyclinics KK</t>
-        </is>
-      </c>
-      <c r="D43" s="9" t="inlineStr"/>
+          <t>Pharmex</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>088-724989</t>
+        </is>
+      </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
           <t>nan</t>
@@ -1930,20 +1942,20 @@
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="G43" s="8" t="n">
         <v>10</v>
       </c>
       <c r="H43" s="8" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="I43" s="10" t="n">
-        <v>1.44</v>
+        <v>4</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v>28.8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44">
@@ -1952,7 +1964,7 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>TAB PLAVIX (CLOPIDOGREL) 75MG SANOFI</t>
+          <t>TAB CONCOR (BISOPROLOL) 5MG MERCKS</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
@@ -1972,16 +1984,16 @@
         </is>
       </c>
       <c r="G44" s="5" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="I44" s="7" t="n">
-        <v>6.94</v>
+        <v>1.53</v>
       </c>
       <c r="J44" s="7" t="n">
-        <v>430.28</v>
+        <v>30.6</v>
       </c>
     </row>
     <row r="45">
@@ -1990,7 +2002,7 @@
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>TAB YASMIN (DROSPIRENONE 3MG/ ETHINYLESTRADIOL 0.03MG) BAYER</t>
+          <t>SYR BENA EXPECTORANT(DIPHENHYDRAMINE 14MG, AMMONIUM CHLORIDE 135MG/5ML) 90ML XEPA</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
@@ -2006,20 +2018,20 @@
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="G45" s="8" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="H45" s="8" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="I45" s="10" t="n">
-        <v>2.33</v>
+        <v>3.4</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v>48.93</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="46">
@@ -2028,7 +2040,7 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>SYRUP NOVOMIN (DIMENHYDRINATE) 15MG/5ML 60ML (ORANGE FLV) XEPA</t>
+          <t>TAB STORVAS C (ATORVASTATIN) 20MG RANBAXY</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
@@ -2044,20 +2056,20 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="G46" s="5" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="H46" s="5" t="n">
-        <v>7</v>
+        <v>100</v>
       </c>
       <c r="I46" s="7" t="n">
-        <v>5.5</v>
+        <v>0.68</v>
       </c>
       <c r="J46" s="7" t="n">
-        <v>38.5</v>
+        <v>68</v>
       </c>
     </row>
     <row r="47">
@@ -2066,19 +2078,15 @@
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>FLANIL (METHYL SALICYLATE 10.20%, W/W, EUGENOL 1.36% W/W, MENTHOL 5.44% W/W) CREAM 30G MEDISPEC</t>
+          <t>TAB DIAPO (DIAZEPAM) 5MG DUOPHARMA</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>Pahang Pharmacy</t>
-        </is>
-      </c>
-      <c r="D47" s="9" t="inlineStr">
-        <is>
-          <t>016-2160526  |  account2@pahangpharmacy.com.my</t>
-        </is>
-      </c>
+          <t>Permai Polyclinics KK</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="inlineStr"/>
       <c r="E47" s="8" t="inlineStr">
         <is>
           <t>nan</t>
@@ -2086,20 +2094,20 @@
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="G47" s="8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H47" s="8" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I47" s="10" t="n">
-        <v>7.9</v>
+        <v>1.44</v>
       </c>
       <c r="J47" s="10" t="n">
-        <v>134.3</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="48">
@@ -2108,12 +2116,12 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>TAB NORMATEN (ATENOLOL) 100MG XEPA</t>
+          <t>TAB DESLORATADINE 5MG SYNERRV</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>Permai Polyclinics KK</t>
+          <t>Dr. Nicholas Neelan Jeremiah</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr"/>
@@ -2128,16 +2136,16 @@
         </is>
       </c>
       <c r="G48" s="5" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H48" s="5" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="I48" s="7" t="n">
-        <v>0.52</v>
+        <v>0</v>
       </c>
       <c r="J48" s="7" t="n">
-        <v>12.48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -2146,15 +2154,19 @@
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>TAB COAPROVEL (IRBESARTAN/ HYDROCHOLOTHIAZIDE) 150MG/12.5MG SANOFI</t>
+          <t>CANDID (CLOTRIMAZOLE 1% W/W) CREAM  20G GLENMARK</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>Permai Polyclinics KK</t>
-        </is>
-      </c>
-      <c r="D49" s="9" t="inlineStr"/>
+          <t>Pharmaforte</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>03-7805 2763  |  pfmy_orders@pharmafortegroup.com</t>
+        </is>
+      </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
           <t>nan</t>
@@ -2162,20 +2174,20 @@
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>TABLET</t>
+          <t>TUBE</t>
         </is>
       </c>
       <c r="G49" s="8" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="H49" s="8" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="I49" s="10" t="n">
-        <v>1.82</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v>43.68</v>
+        <v>9.390000000000001</v>
       </c>
     </row>
     <row r="50">
@@ -2184,7 +2196,7 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>TAB ZENTEL (ALBENDAZOLE) 200MG 2'S HALEON</t>
+          <t>TAB PLAVIX (CLOPIDOGREL) 75MG SANOFI</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
@@ -2200,20 +2212,20 @@
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>PACKET</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="G50" s="5" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="H50" s="5" t="n">
-        <v>4</v>
+        <v>72</v>
       </c>
       <c r="I50" s="7" t="n">
-        <v>9.65</v>
+        <v>6.94</v>
       </c>
       <c r="J50" s="7" t="n">
-        <v>38.6</v>
+        <v>499.68</v>
       </c>
     </row>
     <row r="51">
@@ -2222,7 +2234,7 @@
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>TAB ROWATINEX ( PINENE 31MG, CAMPHENE 31MG, CINEOL 3MG, FENCHONE 4MG, BORNEOL 10MG, ANETHOL 4MG ) DCH AURIGA</t>
+          <t>TAB YASMIN (DROSPIRENONE 3MG/ ETHINYLESTRADIOL 0.03MG) BAYER</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr">
@@ -2242,16 +2254,16 @@
         </is>
       </c>
       <c r="G51" s="8" t="n">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="H51" s="8" t="n">
-        <v>200</v>
+        <v>26</v>
       </c>
       <c r="I51" s="10" t="n">
-        <v>0.66</v>
+        <v>2.33</v>
       </c>
       <c r="J51" s="10" t="n">
-        <v>132</v>
+        <v>60.58</v>
       </c>
     </row>
     <row r="52">
@@ -2260,7 +2272,7 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>CREAM CLODERM (CLOBETASOL 0.05% W/W) 15G HOE</t>
+          <t>SYRUP NOVOMIN (DIMENHYDRINATE) 15MG/5ML 60ML (ORANGE FLV) XEPA</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
@@ -2276,20 +2288,20 @@
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="G52" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H52" s="5" t="n">
         <v>7</v>
       </c>
       <c r="I52" s="7" t="n">
-        <v>10.5</v>
+        <v>5.5</v>
       </c>
       <c r="J52" s="7" t="n">
-        <v>73.5</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="53">
@@ -2298,18 +2310,22 @@
       </c>
       <c r="B53" s="9" t="inlineStr">
         <is>
-          <t>ALLERGOCROM  (SODIUM CROMOGLYCATE ) 2% EYE DROPS 10ML PHARMAFORTE URSAPHARM</t>
+          <t>FLANIL (METHYL SALICYLATE 10.20%, W/W, EUGENOL 1.36% W/W, MENTHOL 5.44% W/W) CREAM 30G MEDISPEC</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>Permai Polyclinics KK</t>
-        </is>
-      </c>
-      <c r="D53" s="9" t="inlineStr"/>
+          <t>Pahang Pharmacy</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="inlineStr">
+        <is>
+          <t>016-2160526  |  account2@pahangpharmacy.com.my</t>
+        </is>
+      </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>PHARMAFORTE</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
@@ -2318,16 +2334,16 @@
         </is>
       </c>
       <c r="G53" s="8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H53" s="8" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="I53" s="10" t="n">
-        <v>16.5</v>
+        <v>7.9</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>115.5</v>
+        <v>134.3</v>
       </c>
     </row>
     <row r="54">
@@ -2336,7 +2352,7 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>AQUA CREAM (PARAFFIN, WHITE SOFT CREAM) 500GM DUOPHARMA</t>
+          <t>TAB NORMATEN (ATENOLOL) 100MG XEPA</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
@@ -2352,20 +2368,20 @@
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>JAR</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="G54" s="5" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="H54" s="5" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="I54" s="7" t="n">
-        <v>17</v>
+        <v>0.52</v>
       </c>
       <c r="J54" s="7" t="n">
-        <v>34</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="55">
@@ -2374,7 +2390,7 @@
       </c>
       <c r="B55" s="9" t="inlineStr">
         <is>
-          <t>INJECSOL MgSO4 (Magnesium Sulfate 50% W/v 2.465G) 5ML VIAL AIN MEDICARE</t>
+          <t>TAB COAPROVEL (IRBESARTAN/ HYDROCHOLOTHIAZIDE) 150MG/12.5MG SANOFI</t>
         </is>
       </c>
       <c r="C55" s="9" t="inlineStr">
@@ -2390,20 +2406,20 @@
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>VIAL</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="G55" s="8" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="H55" s="8" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="I55" s="10" t="n">
-        <v>20</v>
+        <v>1.82</v>
       </c>
       <c r="J55" s="10" t="n">
-        <v>60</v>
+        <v>54.6</v>
       </c>
     </row>
     <row r="56">
@@ -2412,7 +2428,7 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>INJ AMINOPHYLLIN 250MG/10ML FRESENIUS</t>
+          <t>TAB ZENTEL (ALBENDAZOLE) 200MG 2'S HALEON</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
@@ -2428,20 +2444,20 @@
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>VIAL</t>
+          <t>PACKET</t>
         </is>
       </c>
       <c r="G56" s="5" t="n">
         <v>2</v>
       </c>
       <c r="H56" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I56" s="7" t="n">
-        <v>8.5</v>
+        <v>9.65</v>
       </c>
       <c r="J56" s="7" t="n">
-        <v>68</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="57">
@@ -2450,7 +2466,7 @@
       </c>
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>INJ ACIPAN (ATROPINE SULPHATE) 1MG/ML 1ML DUOPHARMA</t>
+          <t>TAB ROWATINEX ( PINENE 31MG, CAMPHENE 31MG, CINEOL 3MG, FENCHONE 4MG, BORNEOL 10MG, ANETHOL 4MG ) DCH AURIGA</t>
         </is>
       </c>
       <c r="C57" s="9" t="inlineStr">
@@ -2466,20 +2482,20 @@
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>VIAL</t>
+          <t>TABLET</t>
         </is>
       </c>
       <c r="G57" s="8" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="H57" s="8" t="n">
-        <v>8</v>
+        <v>230</v>
       </c>
       <c r="I57" s="10" t="n">
-        <v>2.32</v>
+        <v>0.66</v>
       </c>
       <c r="J57" s="10" t="n">
-        <v>18.56</v>
+        <v>151.8</v>
       </c>
     </row>
     <row r="58">
@@ -2488,7 +2504,7 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>INFUSOL N/S 500ML ( SODIUM CHLORIDE 0.9% W/V ) AIN MEDICARE</t>
+          <t>CREAM CLODERM (CLOBETASOL 0.05% W/W) 15G HOE</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
@@ -2504,20 +2520,20 @@
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>TUBE</t>
         </is>
       </c>
       <c r="G58" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H58" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I58" s="7" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="J58" s="7" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
     </row>
     <row r="59">
@@ -2526,7 +2542,7 @@
       </c>
       <c r="B59" s="9" t="inlineStr">
         <is>
-          <t>A SCABS ( PERMETHRIN 5% ) LOTION 30ML HOE</t>
+          <t>ALLERGOCROM  (SODIUM CROMOGLYCATE ) 2% EYE DROPS 10ML PHARMAFORTE URSAPHARM</t>
         </is>
       </c>
       <c r="C59" s="9" t="inlineStr">
@@ -2537,25 +2553,25 @@
       <c r="D59" s="9" t="inlineStr"/>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>PHARMAFORTE</t>
         </is>
       </c>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>TUBE</t>
         </is>
       </c>
       <c r="G59" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H59" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I59" s="10" t="n">
-        <v>11.6</v>
+        <v>16.5</v>
       </c>
       <c r="J59" s="10" t="n">
-        <v>69.59999999999999</v>
+        <v>132</v>
       </c>
     </row>
     <row r="60">
@@ -2564,7 +2580,7 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>T3 MYCIN LOTION (CLINDAMYCIN PHOSPHATE 1%) 30ML HOE</t>
+          <t>AQUA CREAM (PARAFFIN, WHITE SOFT CREAM) 500GM DUOPHARMA</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
@@ -2580,20 +2596,20 @@
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>TUBE</t>
+          <t>JAR</t>
         </is>
       </c>
       <c r="G60" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H60" s="5" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I60" s="7" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="J60" s="7" t="n">
-        <v>243</v>
+        <v>51</v>
       </c>
     </row>
     <row r="61">
@@ -2602,7 +2618,7 @@
       </c>
       <c r="B61" s="9" t="inlineStr">
         <is>
-          <t>KAOLIN-PECTIN (PECTIN 25MG/5ML, LIGHT KAOLIN 1G/5ML) 120ML DYNA</t>
+          <t>INJECSOL MgSO4 (Magnesium Sulfate 50% W/v 2.465G) 5ML VIAL AIN MEDICARE</t>
         </is>
       </c>
       <c r="C61" s="9" t="inlineStr">
@@ -2618,20 +2634,20 @@
       </c>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>VIAL</t>
         </is>
       </c>
       <c r="G61" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H61" s="8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I61" s="10" t="n">
-        <v>4.64</v>
+        <v>20</v>
       </c>
       <c r="J61" s="10" t="n">
-        <v>32.48</v>
+        <v>80</v>
       </c>
     </row>
     <row r="62">
@@ -2640,7 +2656,7 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>NITROSOL SUBLINGUAL AEROSOL SPRAY 400mcg/PER SPRAY VITAMODE</t>
+          <t>INJ AMINOPHYLLIN 250MG/10ML FRESENIUS</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
@@ -2656,20 +2672,20 @@
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>SPRAY</t>
+          <t>VIAL</t>
         </is>
       </c>
       <c r="G62" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H62" s="5" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I62" s="7" t="n">
-        <v>55</v>
+        <v>8.5</v>
       </c>
       <c r="J62" s="7" t="n">
-        <v>110</v>
+        <v>76.5</v>
       </c>
     </row>
     <row r="63">
@@ -2678,7 +2694,7 @@
       </c>
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>GENGIGEL SPRAY ( SODIUM HYALURONATE 0.01% ) 20ML PHARMANIAGA</t>
+          <t>INJ ACIPAN (ATROPINE SULPHATE) 1MG/ML 1ML DUOPHARMA</t>
         </is>
       </c>
       <c r="C63" s="9" t="inlineStr">
@@ -2694,20 +2710,20 @@
       </c>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>VIAL</t>
         </is>
       </c>
       <c r="G63" s="8" t="n">
         <v>2</v>
       </c>
       <c r="H63" s="8" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I63" s="10" t="n">
-        <v>35</v>
+        <v>2.32</v>
       </c>
       <c r="J63" s="10" t="n">
-        <v>105</v>
+        <v>20.88</v>
       </c>
     </row>
     <row r="64">
@@ -2716,7 +2732,7 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>PREVENAR 13 (PNEUMOCOCCAL POLYSACCHARIDE CONJUGATE 13-VALENT) PFIZER</t>
+          <t>INFUSOL N/S 500ML ( SODIUM CHLORIDE 0.9% W/V ) AIN MEDICARE</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
@@ -2732,20 +2748,20 @@
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>DOSE</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="G64" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H64" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I64" s="7" t="n">
-        <v>219</v>
+        <v>0</v>
       </c>
       <c r="J64" s="7" t="n">
-        <v>876</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -2754,19 +2770,15 @@
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>SYR EMCOF-SF (HERBAL COUGH SYRUP) 100ML BioCare Pharmaceutical</t>
+          <t>A SCABS ( PERMETHRIN 5% ) LOTION 30ML HOE</t>
         </is>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>Pharmex</t>
-        </is>
-      </c>
-      <c r="D65" s="9" t="inlineStr">
-        <is>
-          <t>088-724989</t>
-        </is>
-      </c>
+          <t>Permai Polyclinics KK</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="inlineStr"/>
       <c r="E65" s="8" t="inlineStr">
         <is>
           <t>nan</t>
@@ -2778,16 +2790,16 @@
         </is>
       </c>
       <c r="G65" s="8" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="H65" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I65" s="10" t="n">
-        <v>6.2</v>
+        <v>11.6</v>
       </c>
       <c r="J65" s="10" t="n">
-        <v>6.2</v>
+        <v>81.2</v>
       </c>
     </row>
     <row r="66">
@@ -2796,19 +2808,15 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>FC CAP NUTRIFORTE BUFFERED VITAMIN C 1000MG 60's ESPRIT CARE</t>
+          <t>T3 MYCIN LOTION (CLINDAMYCIN PHOSPHATE 1%) 30ML HOE</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>Pharmaforte</t>
-        </is>
-      </c>
-      <c r="D66" s="6" t="inlineStr">
-        <is>
-          <t>03-7805 2763  |  pfmy_orders@pharmafortegroup.com</t>
-        </is>
-      </c>
+          <t>Permai Polyclinics KK</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr"/>
       <c r="E66" s="5" t="inlineStr">
         <is>
           <t>nan</t>
@@ -2816,20 +2824,20 @@
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>BOTTLE</t>
+          <t>TUBE</t>
         </is>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H66" s="5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I66" s="7" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="J66" s="7" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
     </row>
     <row r="67">
@@ -2838,12 +2846,12 @@
       </c>
       <c r="B67" s="9" t="inlineStr">
         <is>
-          <t>INJ AMSUBAC (AMPICILLIN 1000MG/ SULBACTAM 500MG) 1.5 G AVERROES PHARMACEUTICALS SDN. BHD.</t>
+          <t>KAOLIN-PECTIN (PECTIN 25MG/5ML, LIGHT KAOLIN 1G/5ML) 120ML DYNA</t>
         </is>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>Dr. Nicholas Neelan Jeremiah</t>
+          <t>Permai Polyclinics KK</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr"/>
@@ -2854,20 +2862,20 @@
       </c>
       <c r="F67" s="8" t="inlineStr">
         <is>
-          <t>AMPULE</t>
+          <t>BOTTLE</t>
         </is>
       </c>
       <c r="G67" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H67" s="8" t="n">
         <v>8</v>
       </c>
       <c r="I67" s="10" t="n">
-        <v>7.4</v>
+        <v>4.64</v>
       </c>
       <c r="J67" s="10" t="n">
-        <v>59.2</v>
+        <v>37.12</v>
       </c>
     </row>
     <row r="68">
@@ -2876,68 +2884,304 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
+          <t>NITROSOL SUBLINGUAL AEROSOL SPRAY 400mcg/PER SPRAY VITAMODE</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>Permai Polyclinics KK</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr"/>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>SPRAY</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H68" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I68" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="J68" s="7" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="B69" s="9" t="inlineStr">
+        <is>
+          <t>GENGIGEL SPRAY ( SODIUM HYALURONATE 0.01% ) 20ML PHARMANIAGA</t>
+        </is>
+      </c>
+      <c r="C69" s="9" t="inlineStr">
+        <is>
+          <t>Permai Polyclinics KK</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="inlineStr"/>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F69" s="8" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="G69" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H69" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="I69" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="J69" s="10" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>PREVENAR 13 (PNEUMOCOCCAL POLYSACCHARIDE CONJUGATE 13-VALENT) PFIZER</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>Permai Polyclinics KK</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr"/>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>DOSE</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H70" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I70" s="7" t="n">
+        <v>219</v>
+      </c>
+      <c r="J70" s="7" t="n">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="n">
+        <v>62</v>
+      </c>
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t>SYR EMCOF-SF (HERBAL COUGH SYRUP) 100ML BioCare Pharmaceutical</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>Pharmex</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="inlineStr">
+        <is>
+          <t>088-724989</t>
+        </is>
+      </c>
+      <c r="E71" s="8" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F71" s="8" t="inlineStr">
+        <is>
+          <t>BOTTLE</t>
+        </is>
+      </c>
+      <c r="G71" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="H71" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I71" s="10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J71" s="10" t="n">
+        <v>18.6</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>FC CAP NUTRIFORTE BUFFERED VITAMIN C 1000MG 60's ESPRIT CARE</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>Pharmaforte</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>03-7805 2763  |  pfmy_orders@pharmafortegroup.com</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>BOTTLE</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I72" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="8" t="n">
+        <v>64</v>
+      </c>
+      <c r="B73" s="9" t="inlineStr">
+        <is>
+          <t>INJ AMSUBAC (AMPICILLIN 1000MG/ SULBACTAM 500MG) 1.5 G AVERROES PHARMACEUTICALS SDN. BHD.</t>
+        </is>
+      </c>
+      <c r="C73" s="9" t="inlineStr">
+        <is>
+          <t>Dr. Nicholas Neelan Jeremiah</t>
+        </is>
+      </c>
+      <c r="D73" s="9" t="inlineStr"/>
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F73" s="8" t="inlineStr">
+        <is>
+          <t>AMPULE</t>
+        </is>
+      </c>
+      <c r="G73" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H73" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="I73" s="10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J73" s="10" t="n">
+        <v>66.59999999999999</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
           <t>TAB AUROXETIL 500 (Cefuroxime 500 Mg) Aurobindo Pharma</t>
         </is>
       </c>
-      <c r="C68" s="6" t="inlineStr">
+      <c r="C74" s="6" t="inlineStr">
         <is>
           <t>PharmaExpress</t>
         </is>
       </c>
-      <c r="D68" s="6" t="inlineStr">
+      <c r="D74" s="6" t="inlineStr">
         <is>
           <t>088-393227  |  info@pharmaexpress.com.my</t>
         </is>
       </c>
-      <c r="E68" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="F68" s="5" t="inlineStr">
+      <c r="E74" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F74" s="5" t="inlineStr">
         <is>
           <t>TABLET</t>
         </is>
       </c>
-      <c r="G68" s="5" t="n">
+      <c r="G74" s="5" t="n">
         <v>310</v>
       </c>
-      <c r="H68" s="5" t="n">
-        <v>190</v>
-      </c>
-      <c r="I68" s="7" t="n">
+      <c r="H74" s="5" t="n">
+        <v>240</v>
+      </c>
+      <c r="I74" s="7" t="n">
         <v>1.44</v>
       </c>
-      <c r="J68" s="7" t="n">
-        <v>273.6</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="11" t="inlineStr">
+      <c r="J74" s="7" t="n">
+        <v>345.6</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="11" t="inlineStr">
         <is>
           <t>GRAND TOTAL</t>
         </is>
       </c>
-      <c r="J69" s="12" t="n">
-        <v>6453.800000000001</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Total line items: 59</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Generated: 2026-07-02 08:04</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="13" t="inlineStr">
+      <c r="J75" s="12" t="n">
+        <v>7724.540000000002</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Total line items: 65</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Generated: 2026-07-02 13:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="13" t="inlineStr">
         <is>
           <t>Note: Unit costs are from latest purchase price. Verify with supplier before confirming order.</t>
         </is>
@@ -2945,8 +3189,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A69:I69"/>
     <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A75:I75"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
